--- a/Team-Data/2008-09/12-7-2008-09.xlsx
+++ b/Team-Data/2008-09/12-7-2008-09.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -745,7 +812,7 @@
         <v>9</v>
       </c>
       <c r="AF2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AG2" t="n">
         <v>9</v>
@@ -754,7 +821,7 @@
         <v>24</v>
       </c>
       <c r="AI2" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AJ2" t="n">
         <v>22</v>
@@ -787,16 +854,16 @@
         <v>16</v>
       </c>
       <c r="AT2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AU2" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AV2" t="n">
         <v>13</v>
       </c>
       <c r="AW2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AX2" t="n">
         <v>17</v>
@@ -808,10 +875,10 @@
         <v>9</v>
       </c>
       <c r="BA2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BB2" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BC2" t="n">
         <v>12</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>12-7-2008-09</t>
+          <t>2008-12-07</t>
         </is>
       </c>
     </row>
@@ -855,67 +922,67 @@
         <v>0.905</v>
       </c>
       <c r="H3" t="n">
-        <v>48.5</v>
+        <v>48.2</v>
       </c>
       <c r="I3" t="n">
-        <v>36.1</v>
+        <v>35.7</v>
       </c>
       <c r="J3" t="n">
-        <v>76.2</v>
+        <v>75.7</v>
       </c>
       <c r="K3" t="n">
-        <v>0.474</v>
+        <v>0.471</v>
       </c>
       <c r="L3" t="n">
-        <v>5.8</v>
+        <v>5.3</v>
       </c>
       <c r="M3" t="n">
-        <v>16.2</v>
+        <v>15.7</v>
       </c>
       <c r="N3" t="n">
-        <v>0.358</v>
+        <v>0.339</v>
       </c>
       <c r="O3" t="n">
-        <v>22.7</v>
+        <v>22.5</v>
       </c>
       <c r="P3" t="n">
         <v>29.4</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.771</v>
+        <v>0.764</v>
       </c>
       <c r="R3" t="n">
-        <v>10.6</v>
+        <v>10.7</v>
       </c>
       <c r="S3" t="n">
-        <v>32.9</v>
+        <v>32.4</v>
       </c>
       <c r="T3" t="n">
-        <v>43.5</v>
+        <v>43.1</v>
       </c>
       <c r="U3" t="n">
-        <v>21.5</v>
+        <v>21.1</v>
       </c>
       <c r="V3" t="n">
         <v>15.8</v>
       </c>
       <c r="W3" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="X3" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="Y3" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="Z3" t="n">
-        <v>22.6</v>
+        <v>22.7</v>
       </c>
       <c r="AA3" t="n">
         <v>24</v>
       </c>
       <c r="AB3" t="n">
-        <v>100.7</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="AC3" t="n">
         <v>9.4</v>
@@ -933,25 +1000,25 @@
         <v>1</v>
       </c>
       <c r="AH3" t="n">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="AI3" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="AJ3" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AK3" t="n">
         <v>5</v>
       </c>
       <c r="AL3" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="AM3" t="n">
         <v>21</v>
       </c>
       <c r="AN3" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="AO3" t="n">
         <v>3</v>
@@ -960,16 +1027,16 @@
         <v>3</v>
       </c>
       <c r="AQ3" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AR3" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AS3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AT3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AU3" t="n">
         <v>9</v>
@@ -978,22 +1045,22 @@
         <v>23</v>
       </c>
       <c r="AW3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AX3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AY3" t="n">
         <v>6</v>
       </c>
       <c r="AZ3" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BA3" t="n">
         <v>3</v>
       </c>
       <c r="BB3" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="BC3" t="n">
         <v>3</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>12-7-2008-09</t>
+          <t>2008-12-07</t>
         </is>
       </c>
     </row>
@@ -1109,13 +1176,13 @@
         <v>22</v>
       </c>
       <c r="AF4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AG4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AH4" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AI4" t="n">
         <v>30</v>
@@ -1124,7 +1191,7 @@
         <v>30</v>
       </c>
       <c r="AK4" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AL4" t="n">
         <v>23</v>
@@ -1133,19 +1200,19 @@
         <v>24</v>
       </c>
       <c r="AN4" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AO4" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AP4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AQ4" t="n">
         <v>22</v>
       </c>
       <c r="AR4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AS4" t="n">
         <v>30</v>
@@ -1157,7 +1224,7 @@
         <v>28</v>
       </c>
       <c r="AV4" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AW4" t="n">
         <v>10</v>
@@ -1172,7 +1239,7 @@
         <v>22</v>
       </c>
       <c r="BA4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BB4" t="n">
         <v>30</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>12-7-2008-09</t>
+          <t>2008-12-07</t>
         </is>
       </c>
     </row>
@@ -1207,109 +1274,109 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F5" t="n">
         <v>11</v>
       </c>
       <c r="G5" t="n">
-        <v>0.421</v>
+        <v>0.45</v>
       </c>
       <c r="H5" t="n">
         <v>48.3</v>
       </c>
       <c r="I5" t="n">
-        <v>36.5</v>
+        <v>36.4</v>
       </c>
       <c r="J5" t="n">
-        <v>84.09999999999999</v>
+        <v>83.3</v>
       </c>
       <c r="K5" t="n">
-        <v>0.434</v>
+        <v>0.437</v>
       </c>
       <c r="L5" t="n">
         <v>5.7</v>
       </c>
       <c r="M5" t="n">
-        <v>15.4</v>
+        <v>15.2</v>
       </c>
       <c r="N5" t="n">
-        <v>0.37</v>
+        <v>0.372</v>
       </c>
       <c r="O5" t="n">
-        <v>19.4</v>
+        <v>20.1</v>
       </c>
       <c r="P5" t="n">
-        <v>24.1</v>
+        <v>25.1</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.805</v>
+        <v>0.8</v>
       </c>
       <c r="R5" t="n">
-        <v>11.8</v>
+        <v>12</v>
       </c>
       <c r="S5" t="n">
-        <v>30.3</v>
+        <v>30.1</v>
       </c>
       <c r="T5" t="n">
-        <v>42.2</v>
+        <v>42.1</v>
       </c>
       <c r="U5" t="n">
-        <v>19.1</v>
+        <v>19.5</v>
       </c>
       <c r="V5" t="n">
-        <v>15.6</v>
+        <v>15.8</v>
       </c>
       <c r="W5" t="n">
         <v>8.300000000000001</v>
       </c>
       <c r="X5" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="Y5" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="Z5" t="n">
-        <v>22.8</v>
+        <v>22.6</v>
       </c>
       <c r="AA5" t="n">
-        <v>20.8</v>
+        <v>21.3</v>
       </c>
       <c r="AB5" t="n">
-        <v>98</v>
+        <v>98.5</v>
       </c>
       <c r="AC5" t="n">
-        <v>-3.3</v>
+        <v>-2.5</v>
       </c>
       <c r="AD5" t="n">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="AE5" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="AF5" t="n">
+        <v>18</v>
+      </c>
+      <c r="AG5" t="n">
         <v>17</v>
       </c>
-      <c r="AG5" t="n">
-        <v>20</v>
-      </c>
       <c r="AH5" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AI5" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AJ5" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AK5" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AL5" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AM5" t="n">
         <v>22</v>
@@ -1318,46 +1385,46 @@
         <v>12</v>
       </c>
       <c r="AO5" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="AP5" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AQ5" t="n">
         <v>4</v>
       </c>
       <c r="AR5" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AS5" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AT5" t="n">
         <v>12</v>
       </c>
       <c r="AU5" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AV5" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="AW5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AX5" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AY5" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AZ5" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="BA5" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="BB5" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="BC5" t="n">
         <v>20</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>12-7-2008-09</t>
+          <t>2008-12-07</t>
         </is>
       </c>
     </row>
@@ -1389,139 +1456,139 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E6" t="n">
         <v>17</v>
       </c>
       <c r="F6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G6" t="n">
-        <v>0.895</v>
+        <v>0.85</v>
       </c>
       <c r="H6" t="n">
         <v>48</v>
       </c>
       <c r="I6" t="n">
-        <v>38.5</v>
+        <v>38.1</v>
       </c>
       <c r="J6" t="n">
-        <v>79.40000000000001</v>
+        <v>78.8</v>
       </c>
       <c r="K6" t="n">
-        <v>0.485</v>
+        <v>0.483</v>
       </c>
       <c r="L6" t="n">
-        <v>7.1</v>
+        <v>6.9</v>
       </c>
       <c r="M6" t="n">
-        <v>20.3</v>
+        <v>20.1</v>
       </c>
       <c r="N6" t="n">
-        <v>0.35</v>
+        <v>0.344</v>
       </c>
       <c r="O6" t="n">
-        <v>20.3</v>
+        <v>20.5</v>
       </c>
       <c r="P6" t="n">
-        <v>26.2</v>
+        <v>26.5</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.777</v>
+        <v>0.774</v>
       </c>
       <c r="R6" t="n">
-        <v>11.4</v>
+        <v>11.2</v>
       </c>
       <c r="S6" t="n">
-        <v>31.5</v>
+        <v>31.6</v>
       </c>
       <c r="T6" t="n">
         <v>42.8</v>
       </c>
       <c r="U6" t="n">
-        <v>21.2</v>
+        <v>20.9</v>
       </c>
       <c r="V6" t="n">
-        <v>12.9</v>
+        <v>13.4</v>
       </c>
       <c r="W6" t="n">
         <v>8</v>
       </c>
       <c r="X6" t="n">
-        <v>6.7</v>
+        <v>6.5</v>
       </c>
       <c r="Y6" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="Z6" t="n">
-        <v>20.5</v>
+        <v>20.8</v>
       </c>
       <c r="AA6" t="n">
-        <v>20.9</v>
+        <v>21.3</v>
       </c>
       <c r="AB6" t="n">
-        <v>104.5</v>
+        <v>103.5</v>
       </c>
       <c r="AC6" t="n">
-        <v>14.3</v>
+        <v>13.3</v>
       </c>
       <c r="AD6" t="n">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="AE6" t="n">
         <v>2</v>
       </c>
       <c r="AF6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AG6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AH6" t="n">
         <v>24</v>
       </c>
       <c r="AI6" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AJ6" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="AK6" t="n">
         <v>2</v>
       </c>
       <c r="AL6" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="AM6" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AN6" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="AO6" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AP6" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AQ6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AR6" t="n">
         <v>13</v>
       </c>
       <c r="AS6" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AT6" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AU6" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="AV6" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AW6" t="n">
         <v>8</v>
@@ -1533,13 +1600,13 @@
         <v>2</v>
       </c>
       <c r="AZ6" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="BA6" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="BB6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BC6" t="n">
         <v>1</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>12-7-2008-09</t>
+          <t>2008-12-07</t>
         </is>
       </c>
     </row>
@@ -1655,13 +1722,13 @@
         <v>11</v>
       </c>
       <c r="AF7" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AG7" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AH7" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AI7" t="n">
         <v>7</v>
@@ -1685,7 +1752,7 @@
         <v>18</v>
       </c>
       <c r="AP7" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AQ7" t="n">
         <v>5</v>
@@ -1700,7 +1767,7 @@
         <v>1</v>
       </c>
       <c r="AU7" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AV7" t="n">
         <v>10</v>
@@ -1709,19 +1776,19 @@
         <v>13</v>
       </c>
       <c r="AX7" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AY7" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AZ7" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="BA7" t="n">
         <v>26</v>
       </c>
       <c r="BB7" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BC7" t="n">
         <v>10</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>12-7-2008-09</t>
+          <t>2008-12-07</t>
         </is>
       </c>
     </row>
@@ -1834,19 +1901,19 @@
         <v>2</v>
       </c>
       <c r="AE8" t="n">
+        <v>5</v>
+      </c>
+      <c r="AF8" t="n">
         <v>6</v>
       </c>
-      <c r="AF8" t="n">
-        <v>7</v>
-      </c>
       <c r="AG8" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AH8" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AI8" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AJ8" t="n">
         <v>24</v>
@@ -1861,7 +1928,7 @@
         <v>18</v>
       </c>
       <c r="AN8" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AO8" t="n">
         <v>1</v>
@@ -1870,7 +1937,7 @@
         <v>1</v>
       </c>
       <c r="AQ8" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AR8" t="n">
         <v>26</v>
@@ -1882,10 +1949,10 @@
         <v>14</v>
       </c>
       <c r="AU8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV8" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AW8" t="n">
         <v>2</v>
@@ -1894,7 +1961,7 @@
         <v>5</v>
       </c>
       <c r="AY8" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AZ8" t="n">
         <v>21</v>
@@ -1906,7 +1973,7 @@
         <v>5</v>
       </c>
       <c r="BC8" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BD8" t="n">
         <v>10</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>12-7-2008-09</t>
+          <t>2008-12-07</t>
         </is>
       </c>
     </row>
@@ -1935,61 +2002,61 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E9" t="n">
         <v>11</v>
       </c>
       <c r="F9" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G9" t="n">
-        <v>0.579</v>
+        <v>0.611</v>
       </c>
       <c r="H9" t="n">
         <v>48</v>
       </c>
       <c r="I9" t="n">
-        <v>35.7</v>
+        <v>35.5</v>
       </c>
       <c r="J9" t="n">
-        <v>79</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="K9" t="n">
-        <v>0.452</v>
+        <v>0.453</v>
       </c>
       <c r="L9" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="M9" t="n">
-        <v>14.5</v>
+        <v>14.4</v>
       </c>
       <c r="N9" t="n">
-        <v>0.367</v>
+        <v>0.382</v>
       </c>
       <c r="O9" t="n">
-        <v>19.1</v>
+        <v>19.4</v>
       </c>
       <c r="P9" t="n">
-        <v>25</v>
+        <v>25.4</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.762</v>
+        <v>0.764</v>
       </c>
       <c r="R9" t="n">
-        <v>10.9</v>
+        <v>11</v>
       </c>
       <c r="S9" t="n">
-        <v>29.4</v>
+        <v>29.6</v>
       </c>
       <c r="T9" t="n">
-        <v>40.3</v>
+        <v>40.6</v>
       </c>
       <c r="U9" t="n">
-        <v>20.7</v>
+        <v>20.8</v>
       </c>
       <c r="V9" t="n">
-        <v>12.7</v>
+        <v>12.9</v>
       </c>
       <c r="W9" t="n">
         <v>6.9</v>
@@ -1998,91 +2065,91 @@
         <v>5.3</v>
       </c>
       <c r="Y9" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="Z9" t="n">
-        <v>21.6</v>
+        <v>21.5</v>
       </c>
       <c r="AA9" t="n">
-        <v>21.5</v>
+        <v>21.3</v>
       </c>
       <c r="AB9" t="n">
-        <v>95.7</v>
+        <v>95.90000000000001</v>
       </c>
       <c r="AC9" t="n">
-        <v>-0.2</v>
+        <v>0.5</v>
       </c>
       <c r="AD9" t="n">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="AE9" t="n">
         <v>11</v>
       </c>
       <c r="AF9" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AG9" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AH9" t="n">
         <v>24</v>
       </c>
       <c r="AI9" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AJ9" t="n">
+        <v>21</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>15</v>
+      </c>
+      <c r="AL9" t="n">
         <v>19</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>16</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>21</v>
       </c>
       <c r="AM9" t="n">
         <v>25</v>
       </c>
       <c r="AN9" t="n">
+        <v>8</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>15</v>
+      </c>
+      <c r="AP9" t="n">
         <v>13</v>
       </c>
-      <c r="AO9" t="n">
-        <v>16</v>
-      </c>
-      <c r="AP9" t="n">
-        <v>14</v>
-      </c>
       <c r="AQ9" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AR9" t="n">
         <v>17</v>
       </c>
       <c r="AS9" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AT9" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="AU9" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AV9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AW9" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AX9" t="n">
         <v>13</v>
       </c>
       <c r="AY9" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AZ9" t="n">
         <v>17</v>
       </c>
       <c r="BA9" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BB9" t="n">
         <v>22</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>12-7-2008-09</t>
+          <t>2008-12-07</t>
         </is>
       </c>
     </row>
@@ -2207,16 +2274,16 @@
         <v>24</v>
       </c>
       <c r="AH10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AI10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AJ10" t="n">
         <v>2</v>
       </c>
       <c r="AK10" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AL10" t="n">
         <v>20</v>
@@ -2237,7 +2304,7 @@
         <v>24</v>
       </c>
       <c r="AR10" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AS10" t="n">
         <v>21</v>
@@ -2258,7 +2325,7 @@
         <v>3</v>
       </c>
       <c r="AY10" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AZ10" t="n">
         <v>16</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>12-7-2008-09</t>
+          <t>2008-12-07</t>
         </is>
       </c>
     </row>
@@ -2383,34 +2450,34 @@
         <v>7</v>
       </c>
       <c r="AF11" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AG11" t="n">
         <v>7</v>
       </c>
       <c r="AH11" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AI11" t="n">
         <v>29</v>
       </c>
       <c r="AJ11" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AK11" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AL11" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AM11" t="n">
         <v>12</v>
       </c>
       <c r="AN11" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AO11" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AP11" t="n">
         <v>12</v>
@@ -2422,10 +2489,10 @@
         <v>19</v>
       </c>
       <c r="AS11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AT11" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AU11" t="n">
         <v>25</v>
@@ -2434,7 +2501,7 @@
         <v>8</v>
       </c>
       <c r="AW11" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AX11" t="n">
         <v>28</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>12-7-2008-09</t>
+          <t>2008-12-07</t>
         </is>
       </c>
     </row>
@@ -2481,118 +2548,118 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E12" t="n">
         <v>7</v>
       </c>
       <c r="F12" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G12" t="n">
-        <v>0.35</v>
+        <v>0.368</v>
       </c>
       <c r="H12" t="n">
-        <v>48.8</v>
+        <v>48.5</v>
       </c>
       <c r="I12" t="n">
-        <v>38.2</v>
+        <v>37.9</v>
       </c>
       <c r="J12" t="n">
-        <v>85.5</v>
+        <v>85.59999999999999</v>
       </c>
       <c r="K12" t="n">
-        <v>0.446</v>
+        <v>0.443</v>
       </c>
       <c r="L12" t="n">
         <v>7.1</v>
       </c>
       <c r="M12" t="n">
-        <v>20.3</v>
+        <v>20.1</v>
       </c>
       <c r="N12" t="n">
-        <v>0.348</v>
+        <v>0.353</v>
       </c>
       <c r="O12" t="n">
-        <v>16.7</v>
+        <v>16.2</v>
       </c>
       <c r="P12" t="n">
-        <v>21.3</v>
+        <v>20.7</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.784</v>
+        <v>0.779</v>
       </c>
       <c r="R12" t="n">
-        <v>11.6</v>
+        <v>11.9</v>
       </c>
       <c r="S12" t="n">
         <v>33.1</v>
       </c>
       <c r="T12" t="n">
-        <v>44.7</v>
+        <v>45</v>
       </c>
       <c r="U12" t="n">
         <v>22.2</v>
       </c>
       <c r="V12" t="n">
-        <v>16.1</v>
+        <v>15.8</v>
       </c>
       <c r="W12" t="n">
         <v>6.4</v>
       </c>
       <c r="X12" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="Y12" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="Z12" t="n">
-        <v>23.5</v>
+        <v>23.3</v>
       </c>
       <c r="AA12" t="n">
-        <v>21.3</v>
+        <v>20.9</v>
       </c>
       <c r="AB12" t="n">
-        <v>100.1</v>
+        <v>99.2</v>
       </c>
       <c r="AC12" t="n">
-        <v>-2.3</v>
+        <v>-2.1</v>
       </c>
       <c r="AD12" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="AE12" t="n">
         <v>22</v>
       </c>
       <c r="AF12" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AG12" t="n">
         <v>22</v>
       </c>
       <c r="AH12" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AI12" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AJ12" t="n">
         <v>3</v>
       </c>
       <c r="AK12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AL12" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AM12" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AN12" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="AO12" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AP12" t="n">
         <v>28</v>
@@ -2601,10 +2668,10 @@
         <v>7</v>
       </c>
       <c r="AR12" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="AS12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AT12" t="n">
         <v>4</v>
@@ -2613,22 +2680,22 @@
         <v>7</v>
       </c>
       <c r="AV12" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="AW12" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AX12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AY12" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AZ12" t="n">
         <v>28</v>
       </c>
       <c r="BA12" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="BB12" t="n">
         <v>11</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>12-7-2008-09</t>
+          <t>2008-12-07</t>
         </is>
       </c>
     </row>
@@ -2753,16 +2820,16 @@
         <v>28</v>
       </c>
       <c r="AH13" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AI13" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AJ13" t="n">
         <v>9</v>
       </c>
       <c r="AK13" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AL13" t="n">
         <v>22</v>
@@ -2783,13 +2850,13 @@
         <v>29</v>
       </c>
       <c r="AR13" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AS13" t="n">
         <v>24</v>
       </c>
       <c r="AT13" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AU13" t="n">
         <v>21</v>
@@ -2798,7 +2865,7 @@
         <v>17</v>
       </c>
       <c r="AW13" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AX13" t="n">
         <v>2</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>12-7-2008-09</t>
+          <t>2008-12-07</t>
         </is>
       </c>
     </row>
@@ -2860,70 +2927,70 @@
         <v>48</v>
       </c>
       <c r="I14" t="n">
-        <v>40.4</v>
+        <v>40.6</v>
       </c>
       <c r="J14" t="n">
-        <v>84.8</v>
+        <v>85.3</v>
       </c>
       <c r="K14" t="n">
-        <v>0.477</v>
+        <v>0.476</v>
       </c>
       <c r="L14" t="n">
-        <v>6.6</v>
+        <v>6.7</v>
       </c>
       <c r="M14" t="n">
-        <v>17.8</v>
+        <v>17.6</v>
       </c>
       <c r="N14" t="n">
-        <v>0.372</v>
+        <v>0.383</v>
       </c>
       <c r="O14" t="n">
-        <v>21.6</v>
+        <v>20.6</v>
       </c>
       <c r="P14" t="n">
-        <v>28.5</v>
+        <v>27.2</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.756</v>
+        <v>0.757</v>
       </c>
       <c r="R14" t="n">
-        <v>13.3</v>
+        <v>13</v>
       </c>
       <c r="S14" t="n">
-        <v>32.9</v>
+        <v>33.2</v>
       </c>
       <c r="T14" t="n">
         <v>46.2</v>
       </c>
       <c r="U14" t="n">
-        <v>23.3</v>
+        <v>23.1</v>
       </c>
       <c r="V14" t="n">
-        <v>14.6</v>
+        <v>14.1</v>
       </c>
       <c r="W14" t="n">
-        <v>10.1</v>
+        <v>9.9</v>
       </c>
       <c r="X14" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="Y14" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="Z14" t="n">
-        <v>20</v>
+        <v>19.6</v>
       </c>
       <c r="AA14" t="n">
-        <v>22.7</v>
+        <v>22.1</v>
       </c>
       <c r="AB14" t="n">
-        <v>109.1</v>
+        <v>108.6</v>
       </c>
       <c r="AC14" t="n">
-        <v>11.8</v>
+        <v>12.2</v>
       </c>
       <c r="AD14" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AE14" t="n">
         <v>3</v>
@@ -2932,7 +2999,7 @@
         <v>1</v>
       </c>
       <c r="AG14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AH14" t="n">
         <v>24</v>
@@ -2953,22 +3020,22 @@
         <v>13</v>
       </c>
       <c r="AN14" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AO14" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AP14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AQ14" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AR14" t="n">
         <v>3</v>
       </c>
       <c r="AS14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AT14" t="n">
         <v>2</v>
@@ -2977,22 +3044,22 @@
         <v>2</v>
       </c>
       <c r="AV14" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AW14" t="n">
         <v>1</v>
       </c>
       <c r="AX14" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AY14" t="n">
         <v>11</v>
       </c>
       <c r="AZ14" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="BA14" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BB14" t="n">
         <v>1</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>12-7-2008-09</t>
+          <t>2008-12-07</t>
         </is>
       </c>
     </row>
@@ -3117,10 +3184,10 @@
         <v>24</v>
       </c>
       <c r="AH15" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AI15" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AJ15" t="n">
         <v>25</v>
@@ -3141,7 +3208,7 @@
         <v>19</v>
       </c>
       <c r="AP15" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AQ15" t="n">
         <v>20</v>
@@ -3159,7 +3226,7 @@
         <v>30</v>
       </c>
       <c r="AV15" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AW15" t="n">
         <v>12</v>
@@ -3174,7 +3241,7 @@
         <v>26</v>
       </c>
       <c r="BA15" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="BB15" t="n">
         <v>27</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>12-7-2008-09</t>
+          <t>2008-12-07</t>
         </is>
       </c>
     </row>
@@ -3299,7 +3366,7 @@
         <v>16</v>
       </c>
       <c r="AH16" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AI16" t="n">
         <v>10</v>
@@ -3323,13 +3390,13 @@
         <v>24</v>
       </c>
       <c r="AP16" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AQ16" t="n">
         <v>24</v>
       </c>
       <c r="AR16" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AS16" t="n">
         <v>28</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>12-7-2008-09</t>
+          <t>2008-12-07</t>
         </is>
       </c>
     </row>
@@ -3406,64 +3473,64 @@
         <v>48.7</v>
       </c>
       <c r="I17" t="n">
-        <v>35.2</v>
+        <v>35.3</v>
       </c>
       <c r="J17" t="n">
-        <v>82</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="K17" t="n">
-        <v>0.429</v>
+        <v>0.434</v>
       </c>
       <c r="L17" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="M17" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="N17" t="n">
-        <v>0.337</v>
+        <v>0.346</v>
       </c>
       <c r="O17" t="n">
-        <v>20</v>
+        <v>19.9</v>
       </c>
       <c r="P17" t="n">
-        <v>26.2</v>
+        <v>26</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.764</v>
+        <v>0.767</v>
       </c>
       <c r="R17" t="n">
-        <v>13.5</v>
+        <v>13.1</v>
       </c>
       <c r="S17" t="n">
-        <v>30.8</v>
+        <v>30.7</v>
       </c>
       <c r="T17" t="n">
-        <v>44.3</v>
+        <v>43.8</v>
       </c>
       <c r="U17" t="n">
-        <v>20.6</v>
+        <v>20.5</v>
       </c>
       <c r="V17" t="n">
         <v>16.3</v>
       </c>
       <c r="W17" t="n">
-        <v>6.4</v>
+        <v>6.1</v>
       </c>
       <c r="X17" t="n">
         <v>3.6</v>
       </c>
       <c r="Y17" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="Z17" t="n">
-        <v>25.2</v>
+        <v>25.3</v>
       </c>
       <c r="AA17" t="n">
-        <v>23.9</v>
+        <v>23.6</v>
       </c>
       <c r="AB17" t="n">
-        <v>95.2</v>
+        <v>95.40000000000001</v>
       </c>
       <c r="AC17" t="n">
         <v>-1.6</v>
@@ -3478,37 +3545,37 @@
         <v>20</v>
       </c>
       <c r="AG17" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AH17" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AI17" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AJ17" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AK17" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="AL17" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AM17" t="n">
         <v>26</v>
       </c>
       <c r="AN17" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="AO17" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AP17" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AQ17" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AR17" t="n">
         <v>2</v>
@@ -3520,13 +3587,13 @@
         <v>5</v>
       </c>
       <c r="AU17" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AV17" t="n">
         <v>29</v>
       </c>
       <c r="AW17" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AX17" t="n">
         <v>27</v>
@@ -3538,7 +3605,7 @@
         <v>30</v>
       </c>
       <c r="BA17" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BB17" t="n">
         <v>23</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>12-7-2008-09</t>
+          <t>2008-12-07</t>
         </is>
       </c>
     </row>
@@ -3666,16 +3733,16 @@
         <v>1</v>
       </c>
       <c r="AI18" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AJ18" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AK18" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AL18" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AM18" t="n">
         <v>23</v>
@@ -3687,19 +3754,19 @@
         <v>20</v>
       </c>
       <c r="AP18" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AQ18" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AR18" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AS18" t="n">
         <v>26</v>
       </c>
       <c r="AT18" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AU18" t="n">
         <v>6</v>
@@ -3717,7 +3784,7 @@
         <v>26</v>
       </c>
       <c r="AZ18" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BA18" t="n">
         <v>21</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>12-7-2008-09</t>
+          <t>2008-12-07</t>
         </is>
       </c>
     </row>
@@ -3839,22 +3906,22 @@
         <v>11</v>
       </c>
       <c r="AF19" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AG19" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AH19" t="n">
         <v>5</v>
       </c>
       <c r="AI19" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AJ19" t="n">
         <v>15</v>
       </c>
       <c r="AK19" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AL19" t="n">
         <v>6</v>
@@ -3866,28 +3933,28 @@
         <v>6</v>
       </c>
       <c r="AO19" t="n">
+        <v>4</v>
+      </c>
+      <c r="AP19" t="n">
         <v>5</v>
       </c>
-      <c r="AP19" t="n">
-        <v>6</v>
-      </c>
       <c r="AQ19" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AR19" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AS19" t="n">
         <v>17</v>
       </c>
       <c r="AT19" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AU19" t="n">
         <v>26</v>
       </c>
       <c r="AV19" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AW19" t="n">
         <v>25</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>12-7-2008-09</t>
+          <t>2008-12-07</t>
         </is>
       </c>
     </row>
@@ -4030,10 +4097,10 @@
         <v>30</v>
       </c>
       <c r="AI20" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AJ20" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AK20" t="n">
         <v>6</v>
@@ -4045,13 +4112,13 @@
         <v>11</v>
       </c>
       <c r="AN20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AO20" t="n">
         <v>17</v>
       </c>
       <c r="AP20" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AQ20" t="n">
         <v>3</v>
@@ -4084,13 +4151,13 @@
         <v>14</v>
       </c>
       <c r="BA20" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="BB20" t="n">
         <v>18</v>
       </c>
       <c r="BC20" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BD20" t="n">
         <v>10</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>12-7-2008-09</t>
+          <t>2008-12-07</t>
         </is>
       </c>
     </row>
@@ -4119,43 +4186,43 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E21" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F21" t="n">
         <v>11</v>
       </c>
       <c r="G21" t="n">
-        <v>0.45</v>
+        <v>0.421</v>
       </c>
       <c r="H21" t="n">
         <v>48.3</v>
       </c>
       <c r="I21" t="n">
-        <v>38.2</v>
+        <v>38.3</v>
       </c>
       <c r="J21" t="n">
-        <v>87.3</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="K21" t="n">
-        <v>0.437</v>
+        <v>0.436</v>
       </c>
       <c r="L21" t="n">
-        <v>11.1</v>
+        <v>11</v>
       </c>
       <c r="M21" t="n">
-        <v>29.9</v>
+        <v>30.2</v>
       </c>
       <c r="N21" t="n">
-        <v>0.37</v>
+        <v>0.365</v>
       </c>
       <c r="O21" t="n">
-        <v>16.7</v>
+        <v>16.4</v>
       </c>
       <c r="P21" t="n">
-        <v>21.1</v>
+        <v>20.7</v>
       </c>
       <c r="Q21" t="n">
         <v>0.789</v>
@@ -4164,19 +4231,19 @@
         <v>11.1</v>
       </c>
       <c r="S21" t="n">
-        <v>31.9</v>
+        <v>31.4</v>
       </c>
       <c r="T21" t="n">
-        <v>42.9</v>
+        <v>42.5</v>
       </c>
       <c r="U21" t="n">
         <v>22.9</v>
       </c>
       <c r="V21" t="n">
-        <v>15.6</v>
+        <v>15.4</v>
       </c>
       <c r="W21" t="n">
-        <v>7.3</v>
+        <v>7.6</v>
       </c>
       <c r="X21" t="n">
         <v>1.8</v>
@@ -4185,40 +4252,40 @@
         <v>5.1</v>
       </c>
       <c r="Z21" t="n">
-        <v>20</v>
+        <v>19.8</v>
       </c>
       <c r="AA21" t="n">
-        <v>18.4</v>
+        <v>18.1</v>
       </c>
       <c r="AB21" t="n">
         <v>104</v>
       </c>
       <c r="AC21" t="n">
-        <v>-3.6</v>
+        <v>-4.4</v>
       </c>
       <c r="AD21" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="AE21" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="AF21" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AG21" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="AH21" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="AI21" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AJ21" t="n">
         <v>1</v>
       </c>
       <c r="AK21" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AL21" t="n">
         <v>1</v>
@@ -4227,13 +4294,13 @@
         <v>1</v>
       </c>
       <c r="AN21" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AO21" t="n">
+        <v>27</v>
+      </c>
+      <c r="AP21" t="n">
         <v>28</v>
-      </c>
-      <c r="AP21" t="n">
-        <v>29</v>
       </c>
       <c r="AQ21" t="n">
         <v>6</v>
@@ -4242,19 +4309,19 @@
         <v>16</v>
       </c>
       <c r="AS21" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AT21" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AU21" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV21" t="n">
         <v>18</v>
       </c>
       <c r="AW21" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="AX21" t="n">
         <v>30</v>
@@ -4263,13 +4330,13 @@
         <v>18</v>
       </c>
       <c r="AZ21" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="BA21" t="n">
         <v>30</v>
       </c>
       <c r="BB21" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BC21" t="n">
         <v>22</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>12-7-2008-09</t>
+          <t>2008-12-07</t>
         </is>
       </c>
     </row>
@@ -4397,7 +4464,7 @@
         <v>28</v>
       </c>
       <c r="AJ22" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AK22" t="n">
         <v>30</v>
@@ -4409,34 +4476,34 @@
         <v>30</v>
       </c>
       <c r="AN22" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AO22" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AP22" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AQ22" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AR22" t="n">
         <v>15</v>
       </c>
       <c r="AS22" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AT22" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AU22" t="n">
         <v>27</v>
       </c>
       <c r="AV22" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AW22" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AX22" t="n">
         <v>23</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>12-7-2008-09</t>
+          <t>2008-12-07</t>
         </is>
       </c>
     </row>
@@ -4573,7 +4640,7 @@
         <v>4</v>
       </c>
       <c r="AH23" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AI23" t="n">
         <v>25</v>
@@ -4582,7 +4649,7 @@
         <v>23</v>
       </c>
       <c r="AK23" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AL23" t="n">
         <v>3</v>
@@ -4594,7 +4661,7 @@
         <v>20</v>
       </c>
       <c r="AO23" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AP23" t="n">
         <v>4</v>
@@ -4609,7 +4676,7 @@
         <v>6</v>
       </c>
       <c r="AT23" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AU23" t="n">
         <v>29</v>
@@ -4618,7 +4685,7 @@
         <v>16</v>
       </c>
       <c r="AW23" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AX23" t="n">
         <v>1</v>
@@ -4627,16 +4694,16 @@
         <v>3</v>
       </c>
       <c r="AZ23" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="BA23" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BB23" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="BC23" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BD23" t="n">
         <v>10</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>12-7-2008-09</t>
+          <t>2008-12-07</t>
         </is>
       </c>
     </row>
@@ -4752,19 +4819,19 @@
         <v>20</v>
       </c>
       <c r="AG24" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AH24" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AI24" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AJ24" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AK24" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AL24" t="n">
         <v>29</v>
@@ -4776,10 +4843,10 @@
         <v>27</v>
       </c>
       <c r="AO24" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AP24" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AQ24" t="n">
         <v>27</v>
@@ -4797,19 +4864,19 @@
         <v>22</v>
       </c>
       <c r="AV24" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AW24" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AX24" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AY24" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AZ24" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="BA24" t="n">
         <v>29</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>12-7-2008-09</t>
+          <t>2008-12-07</t>
         </is>
       </c>
     </row>
@@ -4937,7 +5004,7 @@
         <v>15</v>
       </c>
       <c r="AH25" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AI25" t="n">
         <v>11</v>
@@ -4949,16 +5016,16 @@
         <v>1</v>
       </c>
       <c r="AL25" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AM25" t="n">
         <v>15</v>
       </c>
       <c r="AN25" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AO25" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AP25" t="n">
         <v>8</v>
@@ -4997,7 +5064,7 @@
         <v>9</v>
       </c>
       <c r="BB25" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BC25" t="n">
         <v>15</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>12-7-2008-09</t>
+          <t>2008-12-07</t>
         </is>
       </c>
     </row>
@@ -5032,52 +5099,52 @@
         <v>21</v>
       </c>
       <c r="E26" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F26" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G26" t="n">
-        <v>0.714</v>
+        <v>0.667</v>
       </c>
       <c r="H26" t="n">
         <v>48.2</v>
       </c>
       <c r="I26" t="n">
-        <v>36.4</v>
+        <v>36</v>
       </c>
       <c r="J26" t="n">
-        <v>78.59999999999999</v>
+        <v>78.7</v>
       </c>
       <c r="K26" t="n">
-        <v>0.463</v>
+        <v>0.458</v>
       </c>
       <c r="L26" t="n">
-        <v>8.4</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="M26" t="n">
         <v>20.4</v>
       </c>
       <c r="N26" t="n">
-        <v>0.414</v>
+        <v>0.409</v>
       </c>
       <c r="O26" t="n">
-        <v>17.5</v>
+        <v>17.2</v>
       </c>
       <c r="P26" t="n">
-        <v>22.6</v>
+        <v>22.5</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.775</v>
+        <v>0.767</v>
       </c>
       <c r="R26" t="n">
-        <v>13.1</v>
+        <v>12.9</v>
       </c>
       <c r="S26" t="n">
-        <v>27.6</v>
+        <v>27.7</v>
       </c>
       <c r="T26" t="n">
-        <v>40.8</v>
+        <v>40.6</v>
       </c>
       <c r="U26" t="n">
         <v>21</v>
@@ -5086,49 +5153,49 @@
         <v>13.2</v>
       </c>
       <c r="W26" t="n">
-        <v>6.9</v>
+        <v>7.1</v>
       </c>
       <c r="X26" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="Y26" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="Z26" t="n">
-        <v>20.7</v>
+        <v>20.8</v>
       </c>
       <c r="AA26" t="n">
         <v>20.4</v>
       </c>
       <c r="AB26" t="n">
-        <v>98.7</v>
+        <v>97.7</v>
       </c>
       <c r="AC26" t="n">
-        <v>5.5</v>
+        <v>4.5</v>
       </c>
       <c r="AD26" t="n">
         <v>2</v>
       </c>
       <c r="AE26" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AF26" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AG26" t="n">
         <v>5</v>
       </c>
       <c r="AH26" t="n">
+        <v>19</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>18</v>
+      </c>
+      <c r="AJ26" t="n">
         <v>20</v>
       </c>
-      <c r="AI26" t="n">
-        <v>14</v>
-      </c>
-      <c r="AJ26" t="n">
-        <v>21</v>
-      </c>
       <c r="AK26" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AL26" t="n">
         <v>4</v>
@@ -5137,37 +5204,37 @@
         <v>5</v>
       </c>
       <c r="AN26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AO26" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AP26" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AQ26" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="AR26" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AS26" t="n">
         <v>29</v>
       </c>
       <c r="AT26" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="AU26" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AV26" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW26" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="AX26" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AY26" t="n">
         <v>1</v>
@@ -5179,10 +5246,10 @@
         <v>22</v>
       </c>
       <c r="BB26" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="BC26" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="BD26" t="n">
         <v>10</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>12-7-2008-09</t>
+          <t>2008-12-07</t>
         </is>
       </c>
     </row>
@@ -5310,10 +5377,10 @@
         <v>14</v>
       </c>
       <c r="AK27" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AL27" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AM27" t="n">
         <v>20</v>
@@ -5325,7 +5392,7 @@
         <v>23</v>
       </c>
       <c r="AP27" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AQ27" t="n">
         <v>8</v>
@@ -5340,13 +5407,13 @@
         <v>26</v>
       </c>
       <c r="AU27" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AV27" t="n">
         <v>28</v>
       </c>
       <c r="AW27" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AX27" t="n">
         <v>24</v>
@@ -5358,7 +5425,7 @@
         <v>27</v>
       </c>
       <c r="BA27" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BB27" t="n">
         <v>20</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>12-7-2008-09</t>
+          <t>2008-12-07</t>
         </is>
       </c>
     </row>
@@ -5477,16 +5544,16 @@
         <v>11</v>
       </c>
       <c r="AF28" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AG28" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AH28" t="n">
         <v>5</v>
       </c>
       <c r="AI28" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AJ28" t="n">
         <v>26</v>
@@ -5513,10 +5580,10 @@
         <v>21</v>
       </c>
       <c r="AR28" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AS28" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AT28" t="n">
         <v>23</v>
@@ -5525,7 +5592,7 @@
         <v>8</v>
       </c>
       <c r="AV28" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW28" t="n">
         <v>30</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>12-7-2008-09</t>
+          <t>2008-12-07</t>
         </is>
       </c>
     </row>
@@ -5575,85 +5642,85 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E29" t="n">
         <v>8</v>
       </c>
       <c r="F29" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G29" t="n">
-        <v>0.421</v>
+        <v>0.444</v>
       </c>
       <c r="H29" t="n">
-        <v>48.5</v>
+        <v>48.6</v>
       </c>
       <c r="I29" t="n">
-        <v>35.6</v>
+        <v>35.5</v>
       </c>
       <c r="J29" t="n">
-        <v>78.90000000000001</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="K29" t="n">
-        <v>0.451</v>
+        <v>0.449</v>
       </c>
       <c r="L29" t="n">
-        <v>6.5</v>
+        <v>6.4</v>
       </c>
       <c r="M29" t="n">
         <v>16.5</v>
       </c>
       <c r="N29" t="n">
-        <v>0.395</v>
+        <v>0.391</v>
       </c>
       <c r="O29" t="n">
-        <v>19.3</v>
+        <v>19.7</v>
       </c>
       <c r="P29" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>0.837</v>
+      </c>
+      <c r="R29" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="S29" t="n">
+        <v>30.1</v>
+      </c>
+      <c r="T29" t="n">
+        <v>38.8</v>
+      </c>
+      <c r="U29" t="n">
         <v>22.9</v>
       </c>
-      <c r="Q29" t="n">
-        <v>0.842</v>
-      </c>
-      <c r="R29" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="S29" t="n">
-        <v>29.9</v>
-      </c>
-      <c r="T29" t="n">
-        <v>38.4</v>
-      </c>
-      <c r="U29" t="n">
-        <v>23.1</v>
-      </c>
       <c r="V29" t="n">
-        <v>14.3</v>
+        <v>14.6</v>
       </c>
       <c r="W29" t="n">
-        <v>6.4</v>
+        <v>6.3</v>
       </c>
       <c r="X29" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="Y29" t="n">
         <v>5.6</v>
       </c>
       <c r="Z29" t="n">
-        <v>18.3</v>
+        <v>18.4</v>
       </c>
       <c r="AA29" t="n">
-        <v>21.2</v>
+        <v>21.4</v>
       </c>
       <c r="AB29" t="n">
         <v>97.09999999999999</v>
       </c>
       <c r="AC29" t="n">
-        <v>-4.9</v>
+        <v>-5.2</v>
       </c>
       <c r="AD29" t="n">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="AE29" t="n">
         <v>20</v>
@@ -5662,22 +5729,22 @@
         <v>17</v>
       </c>
       <c r="AG29" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AH29" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AI29" t="n">
         <v>23</v>
       </c>
       <c r="AJ29" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AK29" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AL29" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AM29" t="n">
         <v>19</v>
@@ -5686,34 +5753,34 @@
         <v>4</v>
       </c>
       <c r="AO29" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="AP29" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="AQ29" t="n">
         <v>1</v>
       </c>
       <c r="AR29" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AS29" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AT29" t="n">
         <v>28</v>
       </c>
       <c r="AU29" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AV29" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AW29" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AX29" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AY29" t="n">
         <v>20</v>
@@ -5722,7 +5789,7 @@
         <v>1</v>
       </c>
       <c r="BA29" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="BB29" t="n">
         <v>19</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>12-7-2008-09</t>
+          <t>2008-12-07</t>
         </is>
       </c>
     </row>
@@ -5844,16 +5911,16 @@
         <v>14</v>
       </c>
       <c r="AG30" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AH30" t="n">
         <v>24</v>
       </c>
       <c r="AI30" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AJ30" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AK30" t="n">
         <v>3</v>
@@ -5865,22 +5932,22 @@
         <v>28</v>
       </c>
       <c r="AN30" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AO30" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AP30" t="n">
         <v>11</v>
       </c>
       <c r="AQ30" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AR30" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AS30" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AT30" t="n">
         <v>13</v>
@@ -5889,7 +5956,7 @@
         <v>1</v>
       </c>
       <c r="AV30" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AW30" t="n">
         <v>3</v>
@@ -5907,7 +5974,7 @@
         <v>6</v>
       </c>
       <c r="BB30" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BC30" t="n">
         <v>9</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>12-7-2008-09</t>
+          <t>2008-12-07</t>
         </is>
       </c>
     </row>
@@ -6017,7 +6084,7 @@
         <v>-4.8</v>
       </c>
       <c r="AD31" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AE31" t="n">
         <v>29</v>
@@ -6029,7 +6096,7 @@
         <v>29</v>
       </c>
       <c r="AH31" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AI31" t="n">
         <v>8</v>
@@ -6041,7 +6108,7 @@
         <v>12</v>
       </c>
       <c r="AL31" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AM31" t="n">
         <v>16</v>
@@ -6059,7 +6126,7 @@
         <v>23</v>
       </c>
       <c r="AR31" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AS31" t="n">
         <v>23</v>
@@ -6068,10 +6135,10 @@
         <v>19</v>
       </c>
       <c r="AU31" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AV31" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AW31" t="n">
         <v>11</v>
@@ -6083,7 +6150,7 @@
         <v>16</v>
       </c>
       <c r="AZ31" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="BA31" t="n">
         <v>25</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>12-7-2008-09</t>
+          <t>2008-12-07</t>
         </is>
       </c>
     </row>
